--- a/output/retirement_plan.xlsx
+++ b/output/retirement_plan.xlsx
@@ -5094,7 +5094,7 @@
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n"/>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="77" t="inlineStr">
         <is>
           <t>CACHE — as of 06/29/2026 09:35 AM</t>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
+          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
+          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
         </is>
       </c>
       <c r="D32" s="3" t="n"/>
@@ -18907,10 +18907,10 @@
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="4" t="n"/>
     </row>
-    <row r="36" ht="60" customHeight="1">
+    <row r="36" ht="75" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>Workbook pricing source: CACHE — as of 06/29/2026 09:35 AM. Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
+          <t>Workbook pricing source: CACHE — as of 06/29/2026 09:35 AM. Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
         </is>
       </c>
       <c r="B36" s="3" t="n"/>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
+          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
         </is>
       </c>
     </row>

--- a/output/retirement_plan.xlsx
+++ b/output/retirement_plan.xlsx
@@ -5094,7 +5094,7 @@
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n"/>
     </row>
-    <row r="5" ht="90" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="77" t="inlineStr">
         <is>
           <t>CACHE — as of 06/29/2026 09:35 AM</t>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
+          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
+          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
         </is>
       </c>
       <c r="D32" s="3" t="n"/>
@@ -18907,10 +18907,10 @@
       <c r="E35" s="3" t="n"/>
       <c r="F35" s="4" t="n"/>
     </row>
-    <row r="36" ht="75" customHeight="1">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>Workbook pricing source: CACHE — as of 06/29/2026 09:35 AM. Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
+          <t>Workbook pricing source: CACHE — as of 06/29/2026 09:35 AM. Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
         </is>
       </c>
       <c r="B36" s="3" t="n"/>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Some symbols used offline fallback pricing; see Holdings Detail by Account for ticker-level sources. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
+          <t>Cached quotes were used as of 06/29/2026 09:35 AM; cache TTL is 24.0 hours. CACHE mode checks the cache before calling live providers; this cache passed its 24.0-hour TTL (expired 06/30/2026 09:35 AM) but was used anyway. Ticker-level source counts: cash: 1, stale_cache_from_fixture_cache: 7.</t>
         </is>
       </c>
     </row>

--- a/output/retirement_plan.xlsx
+++ b/output/retirement_plan.xlsx
@@ -18325,7 +18325,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
@@ -18901,7 +18901,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>Built: 2026-07-02</t>
+          <t>Built: 2026-07-03</t>
         </is>
       </c>
       <c r="B35" s="3" t="n"/>
@@ -23927,7 +23927,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -46902,7 +46902,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>$78,559 actual  |  $156,688 annualized</t>
+          <t>$78,559 actual  |  $155,836 annualized</t>
         </is>
       </c>
     </row>
@@ -46925,7 +46925,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>$178,134 actual  |  $355,294 annualized  |  0 unmapped</t>
+          <t>$178,134 actual  |  $353,363 annualized  |  0 unmapped</t>
         </is>
       </c>
     </row>
@@ -66622,7 +66622,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>BALANCE SHEET — As of 2026-07-02</t>
+          <t>BALANCE SHEET — As of 2026-07-03</t>
         </is>
       </c>
     </row>
@@ -68750,7 +68750,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="43" t="inlineStr">
         <is>
-          <t>CORE SPENDING BREAKDOWN — 2026 YTD  (183 days elapsed)</t>
+          <t>CORE SPENDING BREAKDOWN — 2026 YTD  (184 days elapsed)</t>
         </is>
       </c>
     </row>
@@ -68767,7 +68767,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="44" t="inlineStr">
         <is>
-          <t>YTD core spending — actual (183 days)</t>
+          <t>YTD core spending — actual (184 days)</t>
         </is>
       </c>
       <c r="B3" s="46" t="n">
@@ -68781,17 +68781,17 @@
         </is>
       </c>
       <c r="B4" s="46" t="n">
-        <v>156687.78</v>
+        <v>155836.21</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>Annualized vs model (114%  OVER budget)</t>
+          <t>Annualized vs model (113%  OVER budget)</t>
         </is>
       </c>
       <c r="B5" s="47" t="n">
-        <v>19081.78</v>
+        <v>18230.20999999999</v>
       </c>
     </row>
     <row r="6"/>
@@ -68832,7 +68832,7 @@
         <v>3219.58</v>
       </c>
       <c r="C8" s="49" t="n">
-        <v>6421.57</v>
+        <v>6386.67</v>
       </c>
       <c r="D8" s="50" t="n">
         <v>0.04098320067852593</v>
@@ -68851,7 +68851,7 @@
         <v>1164</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>2321.6</v>
+        <v>2309.03</v>
       </c>
       <c r="D9" s="29" t="n">
         <v>0.01481697786351145</v>
@@ -68868,7 +68868,7 @@
         <v>628.74</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>1254.02</v>
+        <v>1247.23</v>
       </c>
       <c r="D10" s="29" t="n">
         <v>0.008003459331532807</v>
@@ -68885,7 +68885,7 @@
         <v>575.6799999999999</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>1148.19</v>
+        <v>1141.98</v>
       </c>
       <c r="D11" s="29" t="n">
         <v>0.007328039361225318</v>
@@ -68902,7 +68902,7 @@
         <v>405.86</v>
       </c>
       <c r="C12" s="27" t="n">
-        <v>809.49</v>
+        <v>805.1</v>
       </c>
       <c r="D12" s="29" t="n">
         <v>0.005166339034093434</v>
@@ -68919,7 +68919,7 @@
         <v>269.8</v>
       </c>
       <c r="C13" s="27" t="n">
-        <v>538.12</v>
+        <v>535.2</v>
       </c>
       <c r="D13" s="29" t="n">
         <v>0.003434381982453083</v>
@@ -68936,7 +68936,7 @@
         <v>170</v>
       </c>
       <c r="C14" s="27" t="n">
-        <v>339.06</v>
+        <v>337.23</v>
       </c>
       <c r="D14" s="29" t="n">
         <v>0.002163991612368511</v>
@@ -68953,7 +68953,7 @@
         <v>5.5</v>
       </c>
       <c r="C15" s="27" t="n">
-        <v>10.97</v>
+        <v>10.91</v>
       </c>
       <c r="D15" s="29" t="n">
         <v>7.001149334133417e-05</v>
@@ -68970,7 +68970,7 @@
         <v>4046.79</v>
       </c>
       <c r="C16" s="49" t="n">
-        <v>8071.47</v>
+        <v>8027.6</v>
       </c>
       <c r="D16" s="50" t="n">
         <v>0.05151305657068685</v>
@@ -68987,7 +68987,7 @@
         <v>1577.94</v>
       </c>
       <c r="C17" s="27" t="n">
-        <v>3147.2</v>
+        <v>3130.16</v>
       </c>
       <c r="D17" s="29" t="n">
         <v>0.02008617014600451</v>
@@ -69004,7 +69004,7 @@
         <v>1004.85</v>
       </c>
       <c r="C18" s="27" t="n">
-        <v>2004.17</v>
+        <v>1993.32</v>
       </c>
       <c r="D18" s="29" t="n">
         <v>0.01279109983346175</v>
@@ -69021,7 +69021,7 @@
         <v>800.37</v>
       </c>
       <c r="C19" s="27" t="n">
-        <v>1596.34</v>
+        <v>1587.69</v>
       </c>
       <c r="D19" s="29" t="n">
         <v>0.0101881998046552</v>
@@ -69038,7 +69038,7 @@
         <v>301.73</v>
       </c>
       <c r="C20" s="27" t="n">
-        <v>601.8</v>
+        <v>598.54</v>
       </c>
       <c r="D20" s="29" t="n">
         <v>0.003840830524705592</v>
@@ -69055,7 +69055,7 @@
         <v>162.01</v>
       </c>
       <c r="C21" s="27" t="n">
-        <v>323.13</v>
+        <v>321.38</v>
       </c>
       <c r="D21" s="29" t="n">
         <v>0.002062284006587191</v>
@@ -69072,7 +69072,7 @@
         <v>99.73999999999999</v>
       </c>
       <c r="C22" s="27" t="n">
-        <v>198.93</v>
+        <v>197.85</v>
       </c>
       <c r="D22" s="29" t="n">
         <v>0.001269626608339031</v>
@@ -69089,7 +69089,7 @@
         <v>75.70999999999999</v>
       </c>
       <c r="C23" s="27" t="n">
-        <v>151</v>
+        <v>150.19</v>
       </c>
       <c r="D23" s="29" t="n">
         <v>0.0009637400292495289</v>
@@ -69106,7 +69106,7 @@
         <v>24.44</v>
       </c>
       <c r="C24" s="27" t="n">
-        <v>48.75</v>
+        <v>48.48</v>
       </c>
       <c r="D24" s="29" t="n">
         <v>0.0003111056176840376</v>
@@ -69123,7 +69123,7 @@
         <v>1958.74</v>
       </c>
       <c r="C25" s="49" t="n">
-        <v>3906.78</v>
+        <v>3885.54</v>
       </c>
       <c r="D25" s="50" t="n">
         <v>0.02493351135770998</v>
@@ -69142,7 +69142,7 @@
         <v>1116.26</v>
       </c>
       <c r="C26" s="27" t="n">
-        <v>2226.38</v>
+        <v>2214.32</v>
       </c>
       <c r="D26" s="29" t="n">
         <v>0.01420927810130867</v>
@@ -69159,7 +69159,7 @@
         <v>749.99</v>
       </c>
       <c r="C27" s="27" t="n">
-        <v>1495.86</v>
+        <v>1487.76</v>
       </c>
       <c r="D27" s="29" t="n">
         <v>0.009546894525648584</v>
@@ -69176,7 +69176,7 @@
         <v>92.48999999999999</v>
       </c>
       <c r="C28" s="27" t="n">
-        <v>184.47</v>
+        <v>183.47</v>
       </c>
       <c r="D28" s="29" t="n">
         <v>0.001177338730752727</v>
@@ -69193,7 +69193,7 @@
         <v>16116.37</v>
       </c>
       <c r="C29" s="49" t="n">
-        <v>32144.67</v>
+        <v>31969.97</v>
       </c>
       <c r="D29" s="50" t="n">
         <v>0.2051511147166323</v>
@@ -69212,7 +69212,7 @@
         <v>7857.88</v>
       </c>
       <c r="C30" s="27" t="n">
-        <v>15672.54</v>
+        <v>15587.68</v>
       </c>
       <c r="D30" s="29" t="n">
         <v>0.1000258024176369</v>
@@ -69229,7 +69229,7 @@
         <v>7175.5</v>
       </c>
       <c r="C31" s="27" t="n">
-        <v>14311.53</v>
+        <v>14234.04</v>
       </c>
       <c r="D31" s="29" t="n">
         <v>0.09133954008558968</v>
@@ -69246,7 +69246,7 @@
         <v>884.34</v>
       </c>
       <c r="C32" s="27" t="n">
-        <v>1763.82</v>
+        <v>1754.27</v>
       </c>
       <c r="D32" s="29" t="n">
         <v>0.01125708436754099</v>
@@ -69263,7 +69263,7 @@
         <v>198.65</v>
       </c>
       <c r="C33" s="27" t="n">
-        <v>396.21</v>
+        <v>394.06</v>
       </c>
       <c r="D33" s="29" t="n">
         <v>0.002528687845864733</v>
@@ -69280,7 +69280,7 @@
         <v>42411.79</v>
       </c>
       <c r="C34" s="49" t="n">
-        <v>84591.82000000001</v>
+        <v>84132.08</v>
       </c>
       <c r="D34" s="50" t="n">
         <v>0.5398750460325569</v>
@@ -69297,7 +69297,7 @@
         <v>40868.65</v>
       </c>
       <c r="C35" s="27" t="n">
-        <v>81512.52</v>
+        <v>81071.14</v>
       </c>
       <c r="D35" s="29" t="n">
         <v>0.5202318576989666</v>
@@ -69314,7 +69314,7 @@
         <v>813.14</v>
       </c>
       <c r="C36" s="27" t="n">
-        <v>1621.81</v>
+        <v>1613.03</v>
       </c>
       <c r="D36" s="29" t="n">
         <v>0.01035075376283136</v>
@@ -69331,7 +69331,7 @@
         <v>625</v>
       </c>
       <c r="C37" s="27" t="n">
-        <v>1246.56</v>
+        <v>1239.81</v>
       </c>
       <c r="D37" s="29" t="n">
         <v>0.007955851516060701</v>
@@ -69348,7 +69348,7 @@
         <v>105</v>
       </c>
       <c r="C38" s="27" t="n">
-        <v>209.42</v>
+        <v>208.29</v>
       </c>
       <c r="D38" s="29" t="n">
         <v>0.001336583054698198</v>
@@ -69365,7 +69365,7 @@
         <v>8481.84</v>
       </c>
       <c r="C39" s="49" t="n">
-        <v>16917.33</v>
+        <v>16825.39</v>
       </c>
       <c r="D39" s="50" t="n">
         <v>0.1079684153967749</v>
@@ -69384,7 +69384,7 @@
         <v>5076.64</v>
       </c>
       <c r="C40" s="27" t="n">
-        <v>10125.36</v>
+        <v>10070.53</v>
       </c>
       <c r="D40" s="29" t="n">
         <v>0.06462239046479104</v>
@@ -69401,7 +69401,7 @@
         <v>1754.09</v>
       </c>
       <c r="C41" s="27" t="n">
-        <v>3498.53</v>
+        <v>3479.59</v>
       </c>
       <c r="D41" s="29" t="n">
         <v>0.02232844733729106</v>
@@ -69418,7 +69418,7 @@
         <v>614.58</v>
       </c>
       <c r="C42" s="27" t="n">
-        <v>1225.78</v>
+        <v>1219.14</v>
       </c>
       <c r="D42" s="29" t="n">
         <v>0.007823211559584937</v>
@@ -69435,7 +69435,7 @@
         <v>524.77</v>
       </c>
       <c r="C43" s="27" t="n">
-        <v>1046.65</v>
+        <v>1040.99</v>
       </c>
       <c r="D43" s="29" t="n">
         <v>0.006679987520133077</v>
@@ -69452,7 +69452,7 @@
         <v>360</v>
       </c>
       <c r="C44" s="27" t="n">
-        <v>718.02</v>
+        <v>714.13</v>
       </c>
       <c r="D44" s="29" t="n">
         <v>0.004582570473250964</v>
@@ -69469,7 +69469,7 @@
         <v>151.76</v>
       </c>
       <c r="C45" s="27" t="n">
-        <v>302.69</v>
+        <v>301.05</v>
       </c>
       <c r="D45" s="29" t="n">
         <v>0.001931808041723795</v>
@@ -69486,7 +69486,7 @@
         <v>20.6</v>
       </c>
       <c r="C46" s="49" t="n">
-        <v>41.09</v>
+        <v>40.86</v>
       </c>
       <c r="D46" s="50" t="n">
         <v>0.0002622248659693607</v>
@@ -69505,7 +69505,7 @@
         <v>20.6</v>
       </c>
       <c r="C47" s="27" t="n">
-        <v>41.09</v>
+        <v>40.86</v>
       </c>
       <c r="D47" s="29" t="n">
         <v>0.0002622248659693607</v>
@@ -69522,7 +69522,7 @@
         <v>6349.61</v>
       </c>
       <c r="C48" s="49" t="n">
-        <v>12664.52</v>
+        <v>12595.69</v>
       </c>
       <c r="D48" s="50" t="n">
         <v>0.08082648695183069</v>
@@ -69541,7 +69541,7 @@
         <v>6326.62</v>
       </c>
       <c r="C49" s="27" t="n">
-        <v>12618.44</v>
+        <v>12550.12</v>
       </c>
       <c r="D49" s="29" t="n">
         <v>0.08053383890966391</v>
@@ -69558,7 +69558,7 @@
         <v>22.99</v>
       </c>
       <c r="C50" s="27" t="n">
-        <v>45.85</v>
+        <v>45.61</v>
       </c>
       <c r="D50" s="29" t="n">
         <v>0.0002926480421667768</v>
@@ -69576,7 +69576,7 @@
         <v>78558.53</v>
       </c>
       <c r="C52" s="30" t="n">
-        <v>156687.78</v>
+        <v>155836.21</v>
       </c>
       <c r="D52" s="31" t="n">
         <v>1</v>
@@ -70051,14 +70051,14 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="43" t="inlineStr">
         <is>
-          <t>SPENDING SUMMARY — 2026 YTD  (183 days elapsed)</t>
+          <t>SPENDING SUMMARY — 2026 YTD  (184 days elapsed)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>YTD total spending — actual (183 days)</t>
+          <t>YTD total spending — actual (184 days)</t>
         </is>
       </c>
       <c r="B2" s="45" t="n">
@@ -70072,7 +70072,7 @@
         </is>
       </c>
       <c r="B3" s="46" t="n">
-        <v>355294.21</v>
+        <v>353363.26</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -70128,7 +70128,7 @@
         <v>352500.42</v>
       </c>
       <c r="C7" s="58" t="n">
-        <v>703074.61</v>
+        <v>699253.55</v>
       </c>
       <c r="D7" s="59" t="inlineStr"/>
       <c r="E7" s="59" t="inlineStr"/>
@@ -70146,7 +70146,7 @@
         <v>352500.42</v>
       </c>
       <c r="C8" s="61" t="n">
-        <v>703074.61</v>
+        <v>699253.55</v>
       </c>
       <c r="D8" s="62" t="inlineStr"/>
       <c r="E8" s="62" t="inlineStr"/>
@@ -70164,7 +70164,7 @@
         <v>14994.06</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>29906.19</v>
+        <v>29743.65</v>
       </c>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="64" t="inlineStr"/>
@@ -70182,7 +70182,7 @@
         <v>2.88</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>5.74</v>
+        <v>5.71</v>
       </c>
       <c r="D10" s="64" t="inlineStr"/>
       <c r="E10" s="64" t="inlineStr"/>
@@ -70200,7 +70200,7 @@
         <v>6.85</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>13.66</v>
+        <v>13.59</v>
       </c>
       <c r="D11" s="64" t="inlineStr"/>
       <c r="E11" s="64" t="inlineStr"/>
@@ -70218,7 +70218,7 @@
         <v>236950</v>
       </c>
       <c r="C12" s="27" t="n">
-        <v>472605.19</v>
+        <v>470036.68</v>
       </c>
       <c r="D12" s="64" t="inlineStr"/>
       <c r="E12" s="64" t="inlineStr"/>
@@ -70236,7 +70236,7 @@
         <v>100546.63</v>
       </c>
       <c r="C13" s="27" t="n">
-        <v>200543.82</v>
+        <v>199453.91</v>
       </c>
       <c r="D13" s="64" t="inlineStr"/>
       <c r="E13" s="64" t="inlineStr"/>
@@ -70254,13 +70254,13 @@
         <v>73468.7</v>
       </c>
       <c r="C14" s="58" t="n">
-        <v>146535.93</v>
+        <v>145739.54</v>
       </c>
       <c r="D14" s="58" t="n">
         <v>120689</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>25846.92999999999</v>
+        <v>25050.54000000001</v>
       </c>
       <c r="F14" s="60" t="n">
         <v>0.412435460735949</v>
@@ -70276,13 +70276,13 @@
         <v>3219.58</v>
       </c>
       <c r="C15" s="61" t="n">
-        <v>6421.57</v>
+        <v>6386.67</v>
       </c>
       <c r="D15" s="61" t="n">
         <v>6315</v>
       </c>
       <c r="E15" s="66" t="n">
-        <v>106.5699999999997</v>
+        <v>71.67000000000007</v>
       </c>
       <c r="F15" s="63" t="n">
         <v>0.01807394115693141</v>
@@ -70298,13 +70298,13 @@
         <v>575.6799999999999</v>
       </c>
       <c r="C16" s="27" t="n">
-        <v>1148.21</v>
+        <v>1141.97</v>
       </c>
       <c r="D16" s="27" t="n">
         <v>1200</v>
       </c>
       <c r="E16" s="27" t="n">
-        <v>-51.78999999999996</v>
+        <v>-58.02999999999997</v>
       </c>
       <c r="F16" s="29" t="n">
         <v>0.003231727879171281</v>
@@ -70320,13 +70320,13 @@
         <v>1164</v>
       </c>
       <c r="C17" s="27" t="n">
-        <v>2321.64</v>
+        <v>2309.02</v>
       </c>
       <c r="D17" s="27" t="n">
         <v>2400</v>
       </c>
       <c r="E17" s="27" t="n">
-        <v>-78.36000000000013</v>
+        <v>-90.98000000000002</v>
       </c>
       <c r="F17" s="29" t="n">
         <v>0.006534413652298798</v>
@@ -70342,13 +70342,13 @@
         <v>405.86</v>
       </c>
       <c r="C18" s="27" t="n">
-        <v>809.5</v>
+        <v>805.1</v>
       </c>
       <c r="D18" s="27" t="n">
         <v>800</v>
       </c>
       <c r="E18" s="67" t="n">
-        <v>9.5</v>
+        <v>5.100000000000023</v>
       </c>
       <c r="F18" s="29" t="n">
         <v>0.002278399591857379</v>
@@ -70364,13 +70364,13 @@
         <v>170</v>
       </c>
       <c r="C19" s="27" t="n">
-        <v>339.07</v>
+        <v>337.23</v>
       </c>
       <c r="D19" s="27" t="n">
         <v>300</v>
       </c>
       <c r="E19" s="67" t="n">
-        <v>39.06999999999999</v>
+        <v>37.23000000000002</v>
       </c>
       <c r="F19" s="29" t="n">
         <v>0.0009543387636518862</v>
@@ -70386,13 +70386,13 @@
         <v>269.8</v>
       </c>
       <c r="C20" s="27" t="n">
-        <v>538.13</v>
+        <v>535.2</v>
       </c>
       <c r="D20" s="27" t="n">
         <v>600</v>
       </c>
       <c r="E20" s="27" t="n">
-        <v>-61.87</v>
+        <v>-64.79999999999995</v>
       </c>
       <c r="F20" s="29" t="n">
         <v>0.001514591755489876</v>
@@ -70408,13 +70408,13 @@
         <v>5.5</v>
       </c>
       <c r="C21" s="27" t="n">
-        <v>10.97</v>
+        <v>10.91</v>
       </c>
       <c r="D21" s="27" t="n">
         <v>15</v>
       </c>
       <c r="E21" s="27" t="n">
-        <v>-4.029999999999999</v>
+        <v>-4.09</v>
       </c>
       <c r="F21" s="29" t="n">
         <v>3.087566588285514e-05</v>
@@ -70430,13 +70430,13 @@
         <v>628.74</v>
       </c>
       <c r="C22" s="27" t="n">
-        <v>1254.04</v>
+        <v>1247.23</v>
       </c>
       <c r="D22" s="27" t="n">
         <v>1000</v>
       </c>
       <c r="E22" s="67" t="n">
-        <v>254.04</v>
+        <v>247.23</v>
       </c>
       <c r="F22" s="29" t="n">
         <v>0.003529593848579335</v>
@@ -70452,13 +70452,13 @@
         <v>1958.74</v>
       </c>
       <c r="C23" s="61" t="n">
-        <v>3906.78</v>
+        <v>3885.54</v>
       </c>
       <c r="D23" s="61" t="n">
         <v>1910</v>
       </c>
       <c r="E23" s="66" t="n">
-        <v>1996.78</v>
+        <v>1975.54</v>
       </c>
       <c r="F23" s="63" t="n">
         <v>0.01099589123479703</v>
@@ -70474,13 +70474,13 @@
         <v>1116.26</v>
       </c>
       <c r="C24" s="27" t="n">
-        <v>2226.42</v>
+        <v>2214.32</v>
       </c>
       <c r="D24" s="27" t="n">
         <v>1500</v>
       </c>
       <c r="E24" s="67" t="n">
-        <v>726.4200000000001</v>
+        <v>714.3200000000002</v>
       </c>
       <c r="F24" s="29" t="n">
         <v>0.006266412872435615</v>
@@ -70496,13 +70496,13 @@
         <v>749.99</v>
       </c>
       <c r="C25" s="27" t="n">
-        <v>1495.88</v>
+        <v>1487.75</v>
       </c>
       <c r="D25" s="27" t="n">
         <v>210</v>
       </c>
       <c r="E25" s="67" t="n">
-        <v>1285.88</v>
+        <v>1277.75</v>
       </c>
       <c r="F25" s="29" t="n">
         <v>0.00421026193736046</v>
@@ -70518,13 +70518,13 @@
         <v>92.48999999999999</v>
       </c>
       <c r="C26" s="27" t="n">
-        <v>184.47</v>
+        <v>183.47</v>
       </c>
       <c r="D26" s="27" t="n">
         <v>200</v>
       </c>
       <c r="E26" s="27" t="n">
-        <v>-15.53</v>
+        <v>-16.53</v>
       </c>
       <c r="F26" s="29" t="n">
         <v>0.0005192164250009585</v>
@@ -70540,13 +70540,13 @@
         <v>15769.65</v>
       </c>
       <c r="C27" s="61" t="n">
-        <v>31453.13</v>
+        <v>31282.19</v>
       </c>
       <c r="D27" s="61" t="n">
         <v>32200</v>
       </c>
       <c r="E27" s="61" t="n">
-        <v>-746.869999999999</v>
+        <v>-917.8100000000013</v>
       </c>
       <c r="F27" s="63" t="n">
         <v>0.08852698990719392</v>
@@ -70562,13 +70562,13 @@
         <v>198.65</v>
       </c>
       <c r="C28" s="27" t="n">
-        <v>396.21</v>
+        <v>394.06</v>
       </c>
       <c r="D28" s="27" t="n">
         <v>400</v>
       </c>
       <c r="E28" s="27" t="n">
-        <v>-3.79000000000002</v>
+        <v>-5.939999999999998</v>
       </c>
       <c r="F28" s="29" t="n">
         <v>0.001115172914114395</v>
@@ -70584,13 +70584,13 @@
         <v>884.34</v>
       </c>
       <c r="C29" s="27" t="n">
-        <v>1763.85</v>
+        <v>1754.26</v>
       </c>
       <c r="D29" s="27" t="n">
         <v>1800</v>
       </c>
       <c r="E29" s="27" t="n">
-        <v>-36.15000000000009</v>
+        <v>-45.74000000000001</v>
       </c>
       <c r="F29" s="29" t="n">
         <v>0.004964470248517113</v>
@@ -70606,13 +70606,13 @@
         <v>7079.89</v>
       </c>
       <c r="C30" s="27" t="n">
-        <v>14121.09</v>
+        <v>14044.35</v>
       </c>
       <c r="D30" s="27" t="n">
         <v>15000</v>
       </c>
       <c r="E30" s="27" t="n">
-        <v>-878.9099999999999</v>
+        <v>-955.6499999999996</v>
       </c>
       <c r="F30" s="29" t="n">
         <v>0.03974478511406678</v>
@@ -70628,13 +70628,13 @@
         <v>7606.77</v>
       </c>
       <c r="C31" s="27" t="n">
-        <v>15171.97</v>
+        <v>15089.52</v>
       </c>
       <c r="D31" s="27" t="n">
         <v>15000</v>
       </c>
       <c r="E31" s="67" t="n">
-        <v>171.9699999999993</v>
+        <v>89.52000000000044</v>
       </c>
       <c r="F31" s="29" t="n">
         <v>0.04270256163049564</v>
@@ -70650,13 +70650,13 @@
         <v>42411.79</v>
       </c>
       <c r="C32" s="61" t="n">
-        <v>84591.82000000001</v>
+        <v>84132.08</v>
       </c>
       <c r="D32" s="61" t="n">
         <v>49800</v>
       </c>
       <c r="E32" s="66" t="n">
-        <v>34791.82000000001</v>
+        <v>34332.08</v>
       </c>
       <c r="F32" s="63" t="n">
         <v>0.2380895013697849</v>
@@ -70672,13 +70672,13 @@
         <v>105</v>
       </c>
       <c r="C33" s="27" t="n">
-        <v>209.43</v>
+        <v>208.29</v>
       </c>
       <c r="D33" s="27" t="n">
         <v>5000</v>
       </c>
       <c r="E33" s="27" t="n">
-        <v>-4790.57</v>
+        <v>-4791.71</v>
       </c>
       <c r="F33" s="29" t="n">
         <v>0.0005894445304908709</v>
@@ -70694,13 +70694,13 @@
         <v>625</v>
       </c>
       <c r="C34" s="27" t="n">
-        <v>1246.58</v>
+        <v>1239.81</v>
       </c>
       <c r="D34" s="27" t="n">
         <v>1300</v>
       </c>
       <c r="E34" s="27" t="n">
-        <v>-53.42000000000007</v>
+        <v>-60.19000000000005</v>
       </c>
       <c r="F34" s="29" t="n">
         <v>0.003508598395778993</v>
@@ -70716,13 +70716,13 @@
         <v>40868.65</v>
       </c>
       <c r="C35" s="27" t="n">
-        <v>81513.97</v>
+        <v>81070.96000000001</v>
       </c>
       <c r="D35" s="27" t="n">
         <v>42000</v>
       </c>
       <c r="E35" s="67" t="n">
-        <v>39513.97</v>
+        <v>39070.96000000001</v>
       </c>
       <c r="F35" s="29" t="n">
         <v>0.2294266877242451</v>
@@ -70738,13 +70738,13 @@
         <v>813.14</v>
       </c>
       <c r="C36" s="27" t="n">
-        <v>1621.84</v>
+        <v>1613.02</v>
       </c>
       <c r="D36" s="27" t="n">
         <v>1500</v>
       </c>
       <c r="E36" s="67" t="n">
-        <v>121.8399999999999</v>
+        <v>113.02</v>
       </c>
       <c r="F36" s="29" t="n">
         <v>0.004564770719269969</v>
@@ -70760,13 +70760,13 @@
         <v>5822.34</v>
       </c>
       <c r="C37" s="61" t="n">
-        <v>11612.86</v>
+        <v>11549.75</v>
       </c>
       <c r="D37" s="61" t="n">
         <v>14300</v>
       </c>
       <c r="E37" s="61" t="n">
-        <v>-2687.139999999999</v>
+        <v>-2750.25</v>
       </c>
       <c r="F37" s="63" t="n">
         <v>0.03268520445388778</v>
@@ -70782,13 +70782,13 @@
         <v>2417.14</v>
       </c>
       <c r="C38" s="27" t="n">
-        <v>4821.07</v>
+        <v>4794.87</v>
       </c>
       <c r="D38" s="27" t="n">
         <v>8000</v>
       </c>
       <c r="E38" s="27" t="n">
-        <v>-3178.93</v>
+        <v>-3205.13</v>
       </c>
       <c r="F38" s="29" t="n">
         <v>0.01356923764219718</v>
@@ -70804,13 +70804,13 @@
         <v>614.58</v>
       </c>
       <c r="C39" s="27" t="n">
-        <v>1225.8</v>
+        <v>1219.14</v>
       </c>
       <c r="D39" s="27" t="n">
         <v>1000</v>
       </c>
       <c r="E39" s="67" t="n">
-        <v>225.8</v>
+        <v>219.1400000000001</v>
       </c>
       <c r="F39" s="29" t="n">
         <v>0.003450103043324566</v>
@@ -70826,13 +70826,13 @@
         <v>1754.09</v>
       </c>
       <c r="C40" s="27" t="n">
-        <v>3498.59</v>
+        <v>3479.58</v>
       </c>
       <c r="D40" s="27" t="n">
         <v>3500</v>
       </c>
       <c r="E40" s="27" t="n">
-        <v>-1.409999999999854</v>
+        <v>-20.42000000000007</v>
       </c>
       <c r="F40" s="29" t="n">
         <v>0.009847035776083158</v>
@@ -70848,13 +70848,13 @@
         <v>524.77</v>
       </c>
       <c r="C41" s="27" t="n">
-        <v>1046.67</v>
+        <v>1040.98</v>
       </c>
       <c r="D41" s="27" t="n">
         <v>1000</v>
       </c>
       <c r="E41" s="67" t="n">
-        <v>46.67000000000007</v>
+        <v>40.98000000000002</v>
       </c>
       <c r="F41" s="29" t="n">
         <v>0.002945931488244708</v>
@@ -70870,13 +70870,13 @@
         <v>151.76</v>
       </c>
       <c r="C42" s="27" t="n">
-        <v>302.69</v>
+        <v>301.05</v>
       </c>
       <c r="D42" s="27" t="n">
         <v>300</v>
       </c>
       <c r="E42" s="67" t="n">
-        <v>2.689999999999998</v>
+        <v>1.050000000000011</v>
       </c>
       <c r="F42" s="29" t="n">
         <v>0.000851943828069472</v>
@@ -70892,13 +70892,13 @@
         <v>360</v>
       </c>
       <c r="C43" s="27" t="n">
-        <v>718.03</v>
+        <v>714.13</v>
       </c>
       <c r="D43" s="27" t="n">
         <v>500</v>
       </c>
       <c r="E43" s="67" t="n">
-        <v>218.03</v>
+        <v>214.13</v>
       </c>
       <c r="F43" s="29" t="n">
         <v>0.0020209526759687</v>
@@ -70914,13 +70914,13 @@
         <v>20.6</v>
       </c>
       <c r="C44" s="61" t="n">
-        <v>41.09</v>
+        <v>40.86</v>
       </c>
       <c r="D44" s="61" t="n">
         <v>6164</v>
       </c>
       <c r="E44" s="61" t="n">
-        <v>-6122.91</v>
+        <v>-6123.14</v>
       </c>
       <c r="F44" s="63" t="n">
         <v>0.0001156434031248756</v>
@@ -70980,13 +70980,13 @@
         <v>20.6</v>
       </c>
       <c r="C47" s="27" t="n">
-        <v>41.09</v>
+        <v>40.86</v>
       </c>
       <c r="D47" s="27" t="n">
         <v>3857</v>
       </c>
       <c r="E47" s="27" t="n">
-        <v>-3815.91</v>
+        <v>-3816.14</v>
       </c>
       <c r="F47" s="29" t="n">
         <v>0.0001156434031248756</v>
@@ -71002,13 +71002,13 @@
         <v>4266</v>
       </c>
       <c r="C48" s="61" t="n">
-        <v>8508.690000000001</v>
+        <v>8462.450000000001</v>
       </c>
       <c r="D48" s="61" t="n">
         <v>10000</v>
       </c>
       <c r="E48" s="61" t="n">
-        <v>-1491.309999999999</v>
+        <v>-1537.549999999999</v>
       </c>
       <c r="F48" s="63" t="n">
         <v>0.0239482892102291</v>
@@ -71024,13 +71024,13 @@
         <v>4243.01</v>
       </c>
       <c r="C49" s="27" t="n">
-        <v>8462.83</v>
+        <v>8416.84</v>
       </c>
       <c r="D49" s="27" t="n">
         <v>10000</v>
       </c>
       <c r="E49" s="27" t="n">
-        <v>-1537.17</v>
+        <v>-1583.16</v>
       </c>
       <c r="F49" s="29" t="n">
         <v>0.02381922892683876</v>
@@ -71046,7 +71046,7 @@
         <v>22.99</v>
       </c>
       <c r="C50" s="27" t="n">
-        <v>45.85</v>
+        <v>45.61</v>
       </c>
       <c r="D50" s="64" t="inlineStr"/>
       <c r="E50" s="64" t="inlineStr"/>
@@ -71064,13 +71064,13 @@
         <v>18388.85</v>
       </c>
       <c r="C51" s="58" t="n">
-        <v>36677.21</v>
+        <v>36477.88</v>
       </c>
       <c r="D51" s="58" t="n">
         <v>50364</v>
       </c>
       <c r="E51" s="58" t="n">
-        <v>-13686.79</v>
+        <v>-13886.12</v>
       </c>
       <c r="F51" s="60" t="n">
         <v>0.1032305433763529</v>
@@ -71086,13 +71086,13 @@
         <v>8790.610000000001</v>
       </c>
       <c r="C52" s="61" t="n">
-        <v>17533.18</v>
+        <v>17437.89</v>
       </c>
       <c r="D52" s="61" t="n">
         <v>23760</v>
       </c>
       <c r="E52" s="61" t="n">
-        <v>-6226.82</v>
+        <v>-6322.110000000001</v>
       </c>
       <c r="F52" s="63" t="n">
         <v>0.04934835223027004</v>
@@ -71174,13 +71174,13 @@
         <v>8790.610000000001</v>
       </c>
       <c r="C56" s="27" t="n">
-        <v>17533.18</v>
+        <v>17437.89</v>
       </c>
       <c r="D56" s="27" t="n">
         <v>12000</v>
       </c>
       <c r="E56" s="67" t="n">
-        <v>5533.18</v>
+        <v>5437.889999999999</v>
       </c>
       <c r="F56" s="29" t="n">
         <v>0.04934835223027004</v>
@@ -71196,13 +71196,13 @@
         <v>9598.24</v>
       </c>
       <c r="C57" s="61" t="n">
-        <v>19144.03</v>
+        <v>19039.99</v>
       </c>
       <c r="D57" s="61" t="n">
         <v>26604</v>
       </c>
       <c r="E57" s="61" t="n">
-        <v>-7459.970000000001</v>
+        <v>-7564.009999999998</v>
       </c>
       <c r="F57" s="63" t="n">
         <v>0.05388219114608282</v>
@@ -71218,13 +71218,13 @@
         <v>400.9</v>
       </c>
       <c r="C58" s="27" t="n">
-        <v>799.61</v>
+        <v>795.26</v>
       </c>
       <c r="D58" s="27" t="n">
         <v>2900</v>
       </c>
       <c r="E58" s="27" t="n">
-        <v>-2100.39</v>
+        <v>-2104.74</v>
       </c>
       <c r="F58" s="29" t="n">
         <v>0.002250555354988477</v>
@@ -71240,13 +71240,13 @@
         <v>728</v>
       </c>
       <c r="C59" s="27" t="n">
-        <v>1452.02</v>
+        <v>1444.13</v>
       </c>
       <c r="D59" s="27" t="n">
         <v>1527</v>
       </c>
       <c r="E59" s="27" t="n">
-        <v>-74.98000000000002</v>
+        <v>-82.86999999999989</v>
       </c>
       <c r="F59" s="29" t="n">
         <v>0.004086815411403371</v>
@@ -71262,13 +71262,13 @@
         <v>3278.39</v>
       </c>
       <c r="C60" s="27" t="n">
-        <v>6538.87</v>
+        <v>6503.33</v>
       </c>
       <c r="D60" s="27" t="n">
         <v>5000</v>
       </c>
       <c r="E60" s="67" t="n">
-        <v>1538.87</v>
+        <v>1503.33</v>
       </c>
       <c r="F60" s="29" t="n">
         <v>0.01840408623158063</v>
@@ -71284,13 +71284,13 @@
         <v>102.69</v>
       </c>
       <c r="C61" s="27" t="n">
-        <v>204.82</v>
+        <v>203.71</v>
       </c>
       <c r="D61" s="27" t="n">
         <v>485</v>
       </c>
       <c r="E61" s="27" t="n">
-        <v>-280.18</v>
+        <v>-281.29</v>
       </c>
       <c r="F61" s="29" t="n">
         <v>0.0005764767508200717</v>
@@ -71306,13 +71306,13 @@
         <v>1616.25</v>
       </c>
       <c r="C62" s="27" t="n">
-        <v>3223.67</v>
+        <v>3206.15</v>
       </c>
       <c r="D62" s="27" t="n">
         <v>2668</v>
       </c>
       <c r="E62" s="67" t="n">
-        <v>555.6700000000001</v>
+        <v>538.1500000000001</v>
       </c>
       <c r="F62" s="29" t="n">
         <v>0.009073235451484477</v>
@@ -71328,13 +71328,13 @@
         <v>590.45</v>
       </c>
       <c r="C63" s="27" t="n">
-        <v>1177.67</v>
+        <v>1171.27</v>
       </c>
       <c r="D63" s="27" t="n">
         <v>10000</v>
       </c>
       <c r="E63" s="27" t="n">
-        <v>-8822.33</v>
+        <v>-8828.73</v>
       </c>
       <c r="F63" s="29" t="n">
         <v>0.003314643076460331</v>
@@ -71350,13 +71350,13 @@
         <v>1335</v>
       </c>
       <c r="C64" s="27" t="n">
-        <v>2662.7</v>
+        <v>2648.23</v>
       </c>
       <c r="D64" s="27" t="n">
         <v>2100</v>
       </c>
       <c r="E64" s="67" t="n">
-        <v>562.6999999999998</v>
+        <v>548.23</v>
       </c>
       <c r="F64" s="29" t="n">
         <v>0.00749436617338393</v>
@@ -71372,13 +71372,13 @@
         <v>1546.56</v>
       </c>
       <c r="C65" s="27" t="n">
-        <v>3084.67</v>
+        <v>3067.9</v>
       </c>
       <c r="D65" s="27" t="n">
         <v>1924</v>
       </c>
       <c r="E65" s="67" t="n">
-        <v>1160.67</v>
+        <v>1143.9</v>
       </c>
       <c r="F65" s="29" t="n">
         <v>0.008682012695961536</v>
@@ -71394,13 +71394,13 @@
         <v>66947.95</v>
       </c>
       <c r="C66" s="58" t="n">
-        <v>133530.06</v>
+        <v>132804.36</v>
       </c>
       <c r="D66" s="58" t="n">
         <v>105600</v>
       </c>
       <c r="E66" s="65" t="n">
-        <v>27930.06</v>
+        <v>27204.35999999999</v>
       </c>
       <c r="F66" s="60" t="n">
         <v>0.3758295519531076</v>
@@ -71416,13 +71416,13 @@
         <v>25689.11</v>
       </c>
       <c r="C67" s="61" t="n">
-        <v>51237.84</v>
+        <v>50959.38</v>
       </c>
       <c r="D67" s="61" t="n">
         <v>25000</v>
       </c>
       <c r="E67" s="66" t="n">
-        <v>26237.84</v>
+        <v>25959.38</v>
       </c>
       <c r="F67" s="63" t="n">
         <v>0.1442124322159841</v>
@@ -71438,13 +71438,13 @@
         <v>25689.11</v>
       </c>
       <c r="C68" s="27" t="n">
-        <v>51237.84</v>
+        <v>50959.38</v>
       </c>
       <c r="D68" s="27" t="n">
         <v>25000</v>
       </c>
       <c r="E68" s="67" t="n">
-        <v>26237.84</v>
+        <v>25959.38</v>
       </c>
       <c r="F68" s="29" t="n">
         <v>0.1442124322159841</v>
@@ -71460,13 +71460,13 @@
         <v>2214.24</v>
       </c>
       <c r="C69" s="61" t="n">
-        <v>4416.38</v>
+        <v>4392.38</v>
       </c>
       <c r="D69" s="61" t="n">
         <v>2100</v>
       </c>
       <c r="E69" s="66" t="n">
-        <v>2316.38</v>
+        <v>2292.38</v>
       </c>
       <c r="F69" s="63" t="n">
         <v>0.01243020625899148</v>
@@ -71482,13 +71482,13 @@
         <v>2214.24</v>
       </c>
       <c r="C70" s="27" t="n">
-        <v>4416.38</v>
+        <v>4392.38</v>
       </c>
       <c r="D70" s="27" t="n">
         <v>2100</v>
       </c>
       <c r="E70" s="67" t="n">
-        <v>2316.38</v>
+        <v>2292.38</v>
       </c>
       <c r="F70" s="29" t="n">
         <v>0.01243020625899148</v>
@@ -71504,13 +71504,13 @@
         <v>18000</v>
       </c>
       <c r="C71" s="61" t="n">
-        <v>35901.64</v>
+        <v>35706.52</v>
       </c>
       <c r="D71" s="61" t="n">
         <v>36000</v>
       </c>
       <c r="E71" s="61" t="n">
-        <v>-98.36000000000058</v>
+        <v>-293.4800000000032</v>
       </c>
       <c r="F71" s="63" t="n">
         <v>0.101047633798435</v>
@@ -71526,13 +71526,13 @@
         <v>18000</v>
       </c>
       <c r="C72" s="27" t="n">
-        <v>35901.64</v>
+        <v>35706.52</v>
       </c>
       <c r="D72" s="27" t="n">
         <v>36000</v>
       </c>
       <c r="E72" s="27" t="n">
-        <v>-98.36000000000058</v>
+        <v>-293.4800000000032</v>
       </c>
       <c r="F72" s="29" t="n">
         <v>0.101047633798435</v>
@@ -71548,13 +71548,13 @@
         <v>5841.79</v>
       </c>
       <c r="C73" s="61" t="n">
-        <v>11651.66</v>
+        <v>11588.33</v>
       </c>
       <c r="D73" s="61" t="n">
         <v>11315</v>
       </c>
       <c r="E73" s="66" t="n">
-        <v>336.6599999999999</v>
+        <v>273.3299999999999</v>
       </c>
       <c r="F73" s="63" t="n">
         <v>0.03279439203596442</v>
@@ -71570,13 +71570,13 @@
         <v>2149.85</v>
       </c>
       <c r="C74" s="27" t="n">
-        <v>4287.95</v>
+        <v>4264.65</v>
       </c>
       <c r="D74" s="27" t="n">
         <v>2115</v>
       </c>
       <c r="E74" s="67" t="n">
-        <v>2172.95</v>
+        <v>2149.65</v>
       </c>
       <c r="F74" s="29" t="n">
         <v>0.01206873641786475</v>
@@ -71614,13 +71614,13 @@
         <v>1600</v>
       </c>
       <c r="C76" s="27" t="n">
-        <v>3191.26</v>
+        <v>3173.91</v>
       </c>
       <c r="D76" s="27" t="n">
         <v>4800</v>
       </c>
       <c r="E76" s="27" t="n">
-        <v>-1608.74</v>
+        <v>-1626.09</v>
       </c>
       <c r="F76" s="29" t="n">
         <v>0.008982011893194223</v>
@@ -71636,13 +71636,13 @@
         <v>2091.94</v>
       </c>
       <c r="C77" s="27" t="n">
-        <v>4172.45</v>
+        <v>4149.77</v>
       </c>
       <c r="D77" s="27" t="n">
         <v>2400</v>
       </c>
       <c r="E77" s="67" t="n">
-        <v>1772.45</v>
+        <v>1749.77</v>
       </c>
       <c r="F77" s="29" t="n">
         <v>0.01174364372490545</v>
@@ -71658,13 +71658,13 @@
         <v>8645.74</v>
       </c>
       <c r="C78" s="61" t="n">
-        <v>17244.24</v>
+        <v>17150.52</v>
       </c>
       <c r="D78" s="61" t="n">
         <v>18000</v>
       </c>
       <c r="E78" s="61" t="n">
-        <v>-755.7599999999984</v>
+        <v>-849.4799999999996</v>
       </c>
       <c r="F78" s="63" t="n">
         <v>0.04853508719091564</v>
@@ -71680,13 +71680,13 @@
         <v>8645.74</v>
       </c>
       <c r="C79" s="27" t="n">
-        <v>17244.24</v>
+        <v>17150.52</v>
       </c>
       <c r="D79" s="27" t="n">
         <v>18000</v>
       </c>
       <c r="E79" s="27" t="n">
-        <v>-755.7599999999984</v>
+        <v>-849.4799999999996</v>
       </c>
       <c r="F79" s="29" t="n">
         <v>0.04853508719091564</v>
@@ -71702,13 +71702,13 @@
         <v>6557.07</v>
       </c>
       <c r="C80" s="61" t="n">
-        <v>13078.31</v>
+        <v>13007.23</v>
       </c>
       <c r="D80" s="61" t="n">
         <v>13185</v>
       </c>
       <c r="E80" s="61" t="n">
-        <v>-106.6900000000005</v>
+        <v>-177.7700000000004</v>
       </c>
       <c r="F80" s="63" t="n">
         <v>0.0368098004528169</v>
@@ -71724,7 +71724,7 @@
         <v>131.34</v>
       </c>
       <c r="C81" s="27" t="n">
-        <v>261.96</v>
+        <v>260.54</v>
       </c>
       <c r="D81" s="64" t="inlineStr"/>
       <c r="E81" s="64" t="inlineStr"/>
@@ -71742,13 +71742,13 @@
         <v>231.8</v>
       </c>
       <c r="C82" s="27" t="n">
-        <v>462.33</v>
+        <v>459.82</v>
       </c>
       <c r="D82" s="27" t="n">
         <v>475</v>
       </c>
       <c r="E82" s="27" t="n">
-        <v>-12.67000000000002</v>
+        <v>-15.18000000000001</v>
       </c>
       <c r="F82" s="29" t="n">
         <v>0.001301268973026513</v>
@@ -71764,13 +71764,13 @@
         <v>2692.38</v>
       </c>
       <c r="C83" s="27" t="n">
-        <v>5370.05</v>
+        <v>5340.86</v>
       </c>
       <c r="D83" s="27" t="n">
         <v>5500</v>
       </c>
       <c r="E83" s="27" t="n">
-        <v>-129.9499999999998</v>
+        <v>-159.1400000000003</v>
       </c>
       <c r="F83" s="29" t="n">
         <v>0.01511436823812391</v>
@@ -71786,13 +71786,13 @@
         <v>2261</v>
       </c>
       <c r="C84" s="27" t="n">
-        <v>4509.64</v>
+        <v>4485.14</v>
       </c>
       <c r="D84" s="27" t="n">
         <v>4510</v>
       </c>
       <c r="E84" s="27" t="n">
-        <v>-0.3599999999996726</v>
+        <v>-24.85999999999967</v>
       </c>
       <c r="F84" s="29" t="n">
         <v>0.01269270555657009</v>
@@ -71808,13 +71808,13 @@
         <v>319.44</v>
       </c>
       <c r="C85" s="27" t="n">
-        <v>637.13</v>
+        <v>633.67</v>
       </c>
       <c r="D85" s="27" t="n">
         <v>650</v>
       </c>
       <c r="E85" s="27" t="n">
-        <v>-12.87</v>
+        <v>-16.33000000000004</v>
       </c>
       <c r="F85" s="29" t="n">
         <v>0.001793258674476227</v>
@@ -71830,13 +71830,13 @@
         <v>672</v>
       </c>
       <c r="C86" s="27" t="n">
-        <v>1340.33</v>
+        <v>1333.04</v>
       </c>
       <c r="D86" s="27" t="n">
         <v>1350</v>
       </c>
       <c r="E86" s="27" t="n">
-        <v>-9.670000000000073</v>
+        <v>-16.96000000000004</v>
       </c>
       <c r="F86" s="29" t="n">
         <v>0.003772444995141574</v>
@@ -71852,13 +71852,13 @@
         <v>93.34</v>
       </c>
       <c r="C87" s="27" t="n">
-        <v>186.17</v>
+        <v>185.16</v>
       </c>
       <c r="D87" s="27" t="n">
         <v>200</v>
       </c>
       <c r="E87" s="27" t="n">
-        <v>-13.83000000000001</v>
+        <v>-14.84</v>
       </c>
       <c r="F87" s="29" t="n">
         <v>0.000523988118819218</v>
@@ -71874,13 +71874,13 @@
         <v>155.77</v>
       </c>
       <c r="C88" s="27" t="n">
-        <v>310.69</v>
+        <v>309</v>
       </c>
       <c r="D88" s="27" t="n">
         <v>500</v>
       </c>
       <c r="E88" s="27" t="n">
-        <v>-189.31</v>
+        <v>-191</v>
       </c>
       <c r="F88" s="29" t="n">
         <v>0.0008744549953767901</v>
@@ -71896,13 +71896,13 @@
         <v>16222.26</v>
       </c>
       <c r="C89" s="58" t="n">
-        <v>32355.87</v>
+        <v>32180.03</v>
       </c>
       <c r="D89" s="58" t="n">
         <v>41917</v>
       </c>
       <c r="E89" s="58" t="n">
-        <v>-9561.130000000001</v>
+        <v>-9736.970000000001</v>
       </c>
       <c r="F89" s="60" t="n">
         <v>0.09106783265905558</v>
@@ -71918,13 +71918,13 @@
         <v>16222.26</v>
       </c>
       <c r="C90" s="61" t="n">
-        <v>32355.87</v>
+        <v>32180.03</v>
       </c>
       <c r="D90" s="61" t="n">
         <v>41917</v>
       </c>
       <c r="E90" s="61" t="n">
-        <v>-9561.130000000001</v>
+        <v>-9736.970000000001</v>
       </c>
       <c r="F90" s="63" t="n">
         <v>0.09106783265905558</v>
@@ -71940,13 +71940,13 @@
         <v>8761.709999999999</v>
       </c>
       <c r="C91" s="27" t="n">
-        <v>17475.54</v>
+        <v>17380.57</v>
       </c>
       <c r="D91" s="27" t="n">
         <v>3270</v>
       </c>
       <c r="E91" s="67" t="n">
-        <v>14205.54</v>
+        <v>14110.57</v>
       </c>
       <c r="F91" s="29" t="n">
         <v>0.04918611464044922</v>
@@ -71984,13 +71984,13 @@
         <v>3722.02</v>
       </c>
       <c r="C93" s="27" t="n">
-        <v>7423.7</v>
+        <v>7383.35</v>
       </c>
       <c r="D93" s="27" t="n">
         <v>8127</v>
       </c>
       <c r="E93" s="27" t="n">
-        <v>-703.3000000000002</v>
+        <v>-743.6499999999996</v>
       </c>
       <c r="F93" s="29" t="n">
         <v>0.02089451744169173</v>
@@ -72006,13 +72006,13 @@
         <v>2248</v>
       </c>
       <c r="C94" s="27" t="n">
-        <v>4483.72</v>
+        <v>4459.35</v>
       </c>
       <c r="D94" s="27" t="n">
         <v>2617</v>
       </c>
       <c r="E94" s="67" t="n">
-        <v>1866.72</v>
+        <v>1842.35</v>
       </c>
       <c r="F94" s="29" t="n">
         <v>0.01261972670993788</v>
@@ -72028,13 +72028,13 @@
         <v>76</v>
       </c>
       <c r="C95" s="27" t="n">
-        <v>151.58</v>
+        <v>150.76</v>
       </c>
       <c r="D95" s="27" t="n">
         <v>159</v>
       </c>
       <c r="E95" s="27" t="n">
-        <v>-7.419999999999987</v>
+        <v>-8.240000000000009</v>
       </c>
       <c r="F95" s="29" t="n">
         <v>0.0004266455649267256</v>
@@ -72050,13 +72050,13 @@
         <v>1414.53</v>
       </c>
       <c r="C96" s="27" t="n">
-        <v>2821.33</v>
+        <v>2806</v>
       </c>
       <c r="D96" s="27" t="n">
         <v>2744</v>
       </c>
       <c r="E96" s="67" t="n">
-        <v>77.32999999999993</v>
+        <v>62</v>
       </c>
       <c r="F96" s="29" t="n">
         <v>0.007940828302050016</v>
@@ -72126,13 +72126,13 @@
         <v>3106.05</v>
       </c>
       <c r="C100" s="58" t="n">
-        <v>6195.13</v>
+        <v>6161.46</v>
       </c>
       <c r="D100" s="58" t="n">
         <v>27890</v>
       </c>
       <c r="E100" s="58" t="n">
-        <v>-21694.87</v>
+        <v>-21728.54</v>
       </c>
       <c r="F100" s="60" t="n">
         <v>0.01743661127553495</v>
@@ -72148,13 +72148,13 @@
         <v>3106.05</v>
       </c>
       <c r="C101" s="61" t="n">
-        <v>6195.13</v>
+        <v>6161.46</v>
       </c>
       <c r="D101" s="61" t="n">
         <v>27890</v>
       </c>
       <c r="E101" s="61" t="n">
-        <v>-21694.87</v>
+        <v>-21728.54</v>
       </c>
       <c r="F101" s="63" t="n">
         <v>0.01743661127553495</v>
@@ -72170,13 +72170,13 @@
         <v>99.73999999999999</v>
       </c>
       <c r="C102" s="27" t="n">
-        <v>198.93</v>
+        <v>197.85</v>
       </c>
       <c r="D102" s="27" t="n">
         <v>200</v>
       </c>
       <c r="E102" s="27" t="n">
-        <v>-1.069999999999993</v>
+        <v>-2.150000000000006</v>
       </c>
       <c r="F102" s="29" t="n">
         <v>0.0005599161663919948</v>
@@ -72192,13 +72192,13 @@
         <v>-48.27</v>
       </c>
       <c r="C103" s="27" t="n">
-        <v>-96.28</v>
+        <v>-95.75</v>
       </c>
       <c r="D103" s="27" t="n">
         <v>200</v>
       </c>
       <c r="E103" s="27" t="n">
-        <v>-296.28</v>
+        <v>-295.75</v>
       </c>
       <c r="F103" s="29" t="n">
         <v>-0.0002709760713028032</v>
@@ -72214,13 +72214,13 @@
         <v>379.95</v>
       </c>
       <c r="C104" s="27" t="n">
-        <v>757.8200000000001</v>
+        <v>753.71</v>
       </c>
       <c r="D104" s="27" t="n">
         <v>500</v>
       </c>
       <c r="E104" s="67" t="n">
-        <v>257.8200000000001</v>
+        <v>253.71</v>
       </c>
       <c r="F104" s="29" t="n">
         <v>0.002132947136761966</v>
@@ -72236,13 +72236,13 @@
         <v>495</v>
       </c>
       <c r="C105" s="27" t="n">
-        <v>987.3</v>
+        <v>981.9299999999999</v>
       </c>
       <c r="D105" s="27" t="n">
         <v>2000</v>
       </c>
       <c r="E105" s="27" t="n">
-        <v>-1012.7</v>
+        <v>-1018.07</v>
       </c>
       <c r="F105" s="29" t="n">
         <v>0.002778809929456963</v>
@@ -72280,13 +72280,13 @@
         <v>24.44</v>
       </c>
       <c r="C107" s="27" t="n">
-        <v>48.75</v>
+        <v>48.48</v>
       </c>
       <c r="D107" s="27" t="n">
         <v>100</v>
       </c>
       <c r="E107" s="27" t="n">
-        <v>-51.25</v>
+        <v>-51.52</v>
       </c>
       <c r="F107" s="29" t="n">
         <v>0.0001372002316685418</v>
@@ -72302,13 +72302,13 @@
         <v>800.37</v>
       </c>
       <c r="C108" s="27" t="n">
-        <v>1596.37</v>
+        <v>1587.69</v>
       </c>
       <c r="D108" s="27" t="n">
         <v>1700</v>
       </c>
       <c r="E108" s="27" t="n">
-        <v>-103.6300000000001</v>
+        <v>-112.3099999999999</v>
       </c>
       <c r="F108" s="29" t="n">
         <v>0.004493083036847412</v>
@@ -72324,13 +72324,13 @@
         <v>1354.82</v>
       </c>
       <c r="C109" s="27" t="n">
-        <v>2702.24</v>
+        <v>2687.55</v>
       </c>
       <c r="D109" s="27" t="n">
         <v>1500</v>
       </c>
       <c r="E109" s="67" t="n">
-        <v>1202.24</v>
+        <v>1187.55</v>
       </c>
       <c r="F109" s="29" t="n">
         <v>0.007605630845710873</v>
@@ -72347,13 +72347,13 @@
         <v>178133.81</v>
       </c>
       <c r="C111" s="30" t="n">
-        <v>355294.21</v>
+        <v>353363.26</v>
       </c>
       <c r="D111" s="30" t="n">
         <v>346460</v>
       </c>
       <c r="E111" s="68" t="n">
-        <v>8834.210000000021</v>
+        <v>6903.260000000009</v>
       </c>
       <c r="F111" s="31" t="n">
         <v>1</v>
